--- a/DevKit_全盘测试缺陷清单.xlsx
+++ b/DevKit_全盘测试缺陷清单.xlsx
@@ -2472,10 +2472,10 @@
     <xf numFmtId="0" fontId="9" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3246,7 +3246,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr filterMode="1"/>
+  <sheetPr/>
   <dimension ref="A1:K28"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
@@ -3302,7 +3302,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="4" ht="88" hidden="1" customHeight="1" spans="1:11">
+    <row r="4" ht="88" customHeight="1" spans="1:11">
       <c r="A4" s="3" t="s">
         <v>68</v>
       </c>
@@ -3368,8 +3368,8 @@
       <c r="J5" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="K5" s="16" t="s">
-        <v>15</v>
+      <c r="K5" s="15" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="6" ht="88" customHeight="1" spans="1:11">
@@ -3403,8 +3403,8 @@
       <c r="J6" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="K6" s="16" t="s">
-        <v>15</v>
+      <c r="K6" s="15" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="7" ht="88" customHeight="1" spans="1:11">
@@ -3438,8 +3438,8 @@
       <c r="J7" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="K7" s="16" t="s">
-        <v>15</v>
+      <c r="K7" s="15" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="8" ht="88" customHeight="1" spans="1:11">
@@ -3449,7 +3449,7 @@
       <c r="B8" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="C8" s="17" t="s">
+      <c r="C8" s="16" t="s">
         <v>16</v>
       </c>
       <c r="D8" s="5" t="s">
@@ -3473,7 +3473,7 @@
       <c r="J8" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="K8" s="16" t="s">
+      <c r="K8" s="17" t="s">
         <v>15</v>
       </c>
     </row>
@@ -3484,7 +3484,7 @@
       <c r="B9" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="C9" s="17" t="s">
+      <c r="C9" s="16" t="s">
         <v>16</v>
       </c>
       <c r="D9" s="5" t="s">
@@ -3508,7 +3508,7 @@
       <c r="J9" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="K9" s="16" t="s">
+      <c r="K9" s="17" t="s">
         <v>15</v>
       </c>
     </row>
@@ -3543,7 +3543,7 @@
       <c r="J10" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="K10" s="16" t="s">
+      <c r="K10" s="17" t="s">
         <v>15</v>
       </c>
     </row>
@@ -3554,7 +3554,7 @@
       <c r="B11" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="C11" s="17" t="s">
+      <c r="C11" s="16" t="s">
         <v>16</v>
       </c>
       <c r="D11" s="5" t="s">
@@ -3578,7 +3578,7 @@
       <c r="J11" s="4" t="s">
         <v>129</v>
       </c>
-      <c r="K11" s="16" t="s">
+      <c r="K11" s="17" t="s">
         <v>15</v>
       </c>
     </row>
@@ -3613,7 +3613,7 @@
       <c r="J12" s="4" t="s">
         <v>136</v>
       </c>
-      <c r="K12" s="16" t="s">
+      <c r="K12" s="17" t="s">
         <v>15</v>
       </c>
     </row>
@@ -3624,7 +3624,7 @@
       <c r="B13" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="C13" s="17" t="s">
+      <c r="C13" s="16" t="s">
         <v>16</v>
       </c>
       <c r="D13" s="5" t="s">
@@ -3648,7 +3648,7 @@
       <c r="J13" s="4" t="s">
         <v>144</v>
       </c>
-      <c r="K13" s="16" t="s">
+      <c r="K13" s="17" t="s">
         <v>15</v>
       </c>
     </row>
@@ -3683,7 +3683,7 @@
       <c r="J14" s="4" t="s">
         <v>152</v>
       </c>
-      <c r="K14" s="16" t="s">
+      <c r="K14" s="17" t="s">
         <v>15</v>
       </c>
     </row>
@@ -3718,7 +3718,7 @@
       <c r="J15" s="4" t="s">
         <v>160</v>
       </c>
-      <c r="K15" s="16" t="s">
+      <c r="K15" s="17" t="s">
         <v>15</v>
       </c>
     </row>
@@ -3753,7 +3753,7 @@
       <c r="J16" s="4" t="s">
         <v>168</v>
       </c>
-      <c r="K16" s="16" t="s">
+      <c r="K16" s="17" t="s">
         <v>15</v>
       </c>
     </row>
@@ -3788,7 +3788,7 @@
       <c r="J17" s="4" t="s">
         <v>176</v>
       </c>
-      <c r="K17" s="16" t="s">
+      <c r="K17" s="17" t="s">
         <v>15</v>
       </c>
     </row>
@@ -3823,7 +3823,7 @@
       <c r="J18" s="4" t="s">
         <v>184</v>
       </c>
-      <c r="K18" s="16" t="s">
+      <c r="K18" s="17" t="s">
         <v>15</v>
       </c>
     </row>
@@ -3858,7 +3858,7 @@
       <c r="J19" s="4" t="s">
         <v>192</v>
       </c>
-      <c r="K19" s="16" t="s">
+      <c r="K19" s="17" t="s">
         <v>15</v>
       </c>
     </row>
@@ -3893,7 +3893,7 @@
       <c r="J20" s="4" t="s">
         <v>200</v>
       </c>
-      <c r="K20" s="16" t="s">
+      <c r="K20" s="17" t="s">
         <v>15</v>
       </c>
     </row>
@@ -3928,7 +3928,7 @@
       <c r="J21" s="4" t="s">
         <v>208</v>
       </c>
-      <c r="K21" s="16" t="s">
+      <c r="K21" s="17" t="s">
         <v>15</v>
       </c>
     </row>
@@ -3963,7 +3963,7 @@
       <c r="J22" s="4" t="s">
         <v>215</v>
       </c>
-      <c r="K22" s="16" t="s">
+      <c r="K22" s="17" t="s">
         <v>15</v>
       </c>
     </row>
@@ -3998,7 +3998,7 @@
       <c r="J23" s="4" t="s">
         <v>223</v>
       </c>
-      <c r="K23" s="16" t="s">
+      <c r="K23" s="17" t="s">
         <v>15</v>
       </c>
     </row>
@@ -4033,7 +4033,7 @@
       <c r="J24" s="4" t="s">
         <v>231</v>
       </c>
-      <c r="K24" s="16" t="s">
+      <c r="K24" s="17" t="s">
         <v>15</v>
       </c>
     </row>
@@ -4044,7 +4044,7 @@
       <c r="B25" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="C25" s="17" t="s">
+      <c r="C25" s="16" t="s">
         <v>16</v>
       </c>
       <c r="D25" s="5" t="s">
@@ -4068,7 +4068,7 @@
       <c r="J25" s="4" t="s">
         <v>239</v>
       </c>
-      <c r="K25" s="16" t="s">
+      <c r="K25" s="17" t="s">
         <v>15</v>
       </c>
     </row>
@@ -4103,7 +4103,7 @@
       <c r="J26" s="4" t="s">
         <v>247</v>
       </c>
-      <c r="K26" s="16" t="s">
+      <c r="K26" s="17" t="s">
         <v>15</v>
       </c>
     </row>
@@ -4138,7 +4138,7 @@
       <c r="J27" s="4" t="s">
         <v>255</v>
       </c>
-      <c r="K27" s="16" t="s">
+      <c r="K27" s="17" t="s">
         <v>15</v>
       </c>
     </row>
@@ -4173,17 +4173,12 @@
       <c r="J28" s="4" t="s">
         <v>263</v>
       </c>
-      <c r="K28" s="16" t="s">
+      <c r="K28" s="17" t="s">
         <v>15</v>
       </c>
     </row>
   </sheetData>
   <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A3:K28" etc:filterBottomFollowUsedRange="0">
-    <filterColumn colId="10">
-      <filters>
-        <filter val="待修复"/>
-      </filters>
-    </filterColumn>
     <extLst/>
   </autoFilter>
   <mergeCells count="1">

--- a/DevKit_全盘测试缺陷清单.xlsx
+++ b/DevKit_全盘测试缺陷清单.xlsx
@@ -3508,8 +3508,8 @@
       <c r="J9" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="K9" s="17" t="s">
-        <v>15</v>
+      <c r="K9" s="15" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="10" ht="88" customHeight="1" spans="1:11">

--- a/DevKit_全盘测试缺陷清单.xlsx
+++ b/DevKit_全盘测试缺陷清单.xlsx
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="730" uniqueCount="494">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="730" uniqueCount="498">
   <si>
     <t>DevKit 全盘测试 · 缺陷汇总</t>
   </si>
@@ -371,6 +371,9 @@
     <t>补齐串口功能实现，或在功能就绪前先从菜单中隐藏该入口，避免误导用户</t>
   </si>
   <si>
+    <t>待实现</t>
+  </si>
+  <si>
     <t>BUG-006</t>
   </si>
   <si>
@@ -424,6 +427,9 @@
     <t>为 RemoteAddress/RemotePort 添加 OnRemoteAddressChanged/OnRemotePortChanged 变更钩子即时持久化，不依赖窗口关闭时机</t>
   </si>
   <si>
+    <t>不能复现</t>
+  </si>
+  <si>
     <t>BUG-008</t>
   </si>
   <si>
@@ -523,6 +529,9 @@
   </si>
   <si>
     <t>在每条 RunCommand 的回调闭包内重新校验 device == CurrentDevice，不匹配则丢弃</t>
+  </si>
+  <si>
+    <t>设计如此，只处理第一台有效设备</t>
   </si>
   <si>
     <t>BUG-012</t>
@@ -602,6 +611,9 @@
   </si>
   <si>
     <t>增加自定义扫描目录的配置项，或增加一次「全盘搜索 *.png」的兜底扫描</t>
+  </si>
+  <si>
+    <t>不处理</t>
   </si>
   <si>
     <t>BUG-015</t>
@@ -1680,6 +1692,13 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="10"/>
       <color rgb="FF375623"/>
@@ -1742,13 +1761,6 @@
     <font>
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -1898,7 +1910,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="44">
+  <fills count="43">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1955,7 +1967,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFD966"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1992,24 +2016,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2282,19 +2288,19 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="21" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="21" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="21" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="21" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="21" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -2303,7 +2309,7 @@
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -2327,16 +2333,16 @@
     <xf numFmtId="0" fontId="29" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="14" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="16" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="15" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="17" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="15" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="17" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="16" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="33" fillId="18" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="34" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -2345,89 +2351,89 @@
     <xf numFmtId="0" fontId="35" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="36" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="37" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="38" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="38" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="39" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="39" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="40" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="40" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="39" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="39" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="40" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="40" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="40" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="39" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="39" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="40" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="40" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="40" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="39" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="39" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="40" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="40" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="40" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="39" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="39" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="40" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="40" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="40" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="39" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="39" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="40" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="40" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="40" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="39" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="39" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2475,19 +2481,28 @@
     <xf numFmtId="0" fontId="8" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2499,25 +2514,25 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="176" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -2894,17 +2909,17 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:9">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="23" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="21" t="s">
+      <c r="A2" s="24" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:9">
-      <c r="A3" s="21" t="s">
+      <c r="A3" s="24" t="s">
         <v>2</v>
       </c>
     </row>
@@ -2930,111 +2945,111 @@
       <c r="H5" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="I5" s="22" t="s">
+      <c r="I5" s="25" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="6" ht="27" spans="1:9">
-      <c r="A6" s="23" t="s">
+      <c r="A6" s="26" t="s">
         <v>11</v>
       </c>
-      <c r="B6" s="24">
+      <c r="B6" s="27">
         <v>4</v>
       </c>
-      <c r="C6" s="25">
+      <c r="C6" s="28">
         <v>0.16</v>
       </c>
-      <c r="D6" s="26" t="s">
+      <c r="D6" s="29" t="s">
         <v>12</v>
       </c>
-      <c r="E6" s="26" t="s">
+      <c r="E6" s="29" t="s">
         <v>13</v>
       </c>
-      <c r="F6" s="26" t="s">
+      <c r="F6" s="29" t="s">
         <v>14</v>
       </c>
-      <c r="H6" s="27" t="s">
+      <c r="H6" s="30" t="s">
         <v>15</v>
       </c>
-      <c r="I6" s="24">
+      <c r="I6" s="27">
         <v>25</v>
       </c>
     </row>
     <row r="7" ht="27" spans="1:9">
-      <c r="A7" s="28" t="s">
+      <c r="A7" s="31" t="s">
         <v>16</v>
       </c>
-      <c r="B7" s="24">
+      <c r="B7" s="27">
         <v>5</v>
       </c>
-      <c r="C7" s="25">
+      <c r="C7" s="28">
         <v>0.2</v>
       </c>
-      <c r="D7" s="26" t="s">
+      <c r="D7" s="29" t="s">
         <v>17</v>
       </c>
-      <c r="E7" s="26" t="s">
+      <c r="E7" s="29" t="s">
         <v>18</v>
       </c>
-      <c r="F7" s="26" t="s">
+      <c r="F7" s="29" t="s">
         <v>19</v>
       </c>
-      <c r="H7" s="29" t="s">
+      <c r="H7" s="32" t="s">
         <v>20</v>
       </c>
-      <c r="I7" s="24">
+      <c r="I7" s="27">
         <v>0</v>
       </c>
     </row>
     <row r="8" ht="27" spans="1:9">
-      <c r="A8" s="30" t="s">
+      <c r="A8" s="33" t="s">
         <v>21</v>
       </c>
-      <c r="B8" s="24">
+      <c r="B8" s="27">
         <v>10</v>
       </c>
-      <c r="C8" s="25">
+      <c r="C8" s="28">
         <v>0.4</v>
       </c>
-      <c r="D8" s="26" t="s">
+      <c r="D8" s="29" t="s">
         <v>22</v>
       </c>
-      <c r="E8" s="26" t="s">
+      <c r="E8" s="29" t="s">
         <v>23</v>
       </c>
-      <c r="F8" s="26" t="s">
+      <c r="F8" s="29" t="s">
         <v>24</v>
       </c>
-      <c r="H8" s="31" t="s">
+      <c r="H8" s="34" t="s">
         <v>25</v>
       </c>
-      <c r="I8" s="24">
+      <c r="I8" s="27">
         <v>0</v>
       </c>
     </row>
     <row r="9" ht="27" spans="1:9">
-      <c r="A9" s="32" t="s">
+      <c r="A9" s="35" t="s">
         <v>26</v>
       </c>
-      <c r="B9" s="24">
+      <c r="B9" s="27">
         <v>6</v>
       </c>
-      <c r="C9" s="25">
+      <c r="C9" s="28">
         <v>0.24</v>
       </c>
-      <c r="D9" s="26" t="s">
+      <c r="D9" s="29" t="s">
         <v>27</v>
       </c>
-      <c r="E9" s="26" t="s">
+      <c r="E9" s="29" t="s">
         <v>28</v>
       </c>
-      <c r="F9" s="26" t="s">
+      <c r="F9" s="29" t="s">
         <v>29</v>
       </c>
-      <c r="H9" s="33" t="s">
+      <c r="H9" s="36" t="s">
         <v>30</v>
       </c>
-      <c r="I9" s="24">
+      <c r="I9" s="27">
         <v>0</v>
       </c>
     </row>
@@ -3045,158 +3060,158 @@
       <c r="B10" s="10">
         <v>25</v>
       </c>
-      <c r="C10" s="34">
+      <c r="C10" s="37">
         <v>1</v>
       </c>
-      <c r="D10" s="35" t="s">
+      <c r="D10" s="38" t="s">
         <v>32</v>
       </c>
-      <c r="E10" s="35" t="s">
+      <c r="E10" s="38" t="s">
         <v>33</v>
       </c>
       <c r="F10" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="H10" s="36" t="s">
+      <c r="H10" s="39" t="s">
         <v>34</v>
       </c>
-      <c r="I10" s="36">
+      <c r="I10" s="39">
         <v>25</v>
       </c>
     </row>
     <row r="12" spans="1:9">
-      <c r="H12" s="37" t="s">
+      <c r="H12" s="40" t="s">
         <v>35</v>
       </c>
-      <c r="I12" s="37" t="s">
+      <c r="I12" s="40" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="13" spans="1:9">
-      <c r="H13" s="22" t="s">
+      <c r="H13" s="25" t="s">
         <v>36</v>
       </c>
-      <c r="I13" s="24">
+      <c r="I13" s="27">
         <v>3</v>
       </c>
     </row>
     <row r="14" spans="1:9">
-      <c r="H14" s="22" t="s">
+      <c r="H14" s="25" t="s">
         <v>37</v>
       </c>
-      <c r="I14" s="24">
+      <c r="I14" s="27">
         <v>3</v>
       </c>
     </row>
     <row r="15" spans="1:9">
-      <c r="H15" s="22" t="s">
+      <c r="H15" s="25" t="s">
         <v>38</v>
       </c>
-      <c r="I15" s="24">
+      <c r="I15" s="27">
         <v>2</v>
       </c>
     </row>
     <row r="16" spans="1:9">
-      <c r="H16" s="22" t="s">
+      <c r="H16" s="25" t="s">
         <v>39</v>
       </c>
-      <c r="I16" s="24">
+      <c r="I16" s="27">
         <v>2</v>
       </c>
     </row>
     <row r="17" spans="1:9">
-      <c r="H17" s="22" t="s">
+      <c r="H17" s="25" t="s">
         <v>40</v>
       </c>
-      <c r="I17" s="24">
+      <c r="I17" s="27">
         <v>2</v>
       </c>
     </row>
     <row r="18" spans="1:9">
-      <c r="H18" s="22" t="s">
+      <c r="H18" s="25" t="s">
         <v>41</v>
       </c>
-      <c r="I18" s="24">
+      <c r="I18" s="27">
         <v>2</v>
       </c>
     </row>
     <row r="19" spans="1:9">
-      <c r="H19" s="22" t="s">
+      <c r="H19" s="25" t="s">
         <v>42</v>
       </c>
-      <c r="I19" s="24">
+      <c r="I19" s="27">
         <v>2</v>
       </c>
     </row>
     <row r="20" spans="1:9">
-      <c r="H20" s="22" t="s">
+      <c r="H20" s="25" t="s">
         <v>43</v>
       </c>
-      <c r="I20" s="24">
+      <c r="I20" s="27">
         <v>2</v>
       </c>
     </row>
     <row r="21" spans="1:9">
-      <c r="H21" s="22" t="s">
+      <c r="H21" s="25" t="s">
         <v>44</v>
       </c>
-      <c r="I21" s="24">
+      <c r="I21" s="27">
         <v>1</v>
       </c>
     </row>
     <row r="22" spans="1:9">
-      <c r="H22" s="22" t="s">
+      <c r="H22" s="25" t="s">
         <v>45</v>
       </c>
-      <c r="I22" s="24">
+      <c r="I22" s="27">
         <v>1</v>
       </c>
     </row>
     <row r="23" spans="1:9">
-      <c r="H23" s="22" t="s">
+      <c r="H23" s="25" t="s">
         <v>46</v>
       </c>
-      <c r="I23" s="24">
+      <c r="I23" s="27">
         <v>1</v>
       </c>
     </row>
     <row r="24" spans="1:9">
-      <c r="H24" s="22" t="s">
+      <c r="H24" s="25" t="s">
         <v>47</v>
       </c>
-      <c r="I24" s="24">
+      <c r="I24" s="27">
         <v>1</v>
       </c>
     </row>
     <row r="25" spans="1:9">
-      <c r="H25" s="22" t="s">
+      <c r="H25" s="25" t="s">
         <v>48</v>
       </c>
-      <c r="I25" s="24">
+      <c r="I25" s="27">
         <v>1</v>
       </c>
     </row>
     <row r="26" spans="1:9">
-      <c r="H26" s="22" t="s">
+      <c r="H26" s="25" t="s">
         <v>49</v>
       </c>
-      <c r="I26" s="24">
+      <c r="I26" s="27">
         <v>1</v>
       </c>
     </row>
     <row r="27" spans="1:9">
-      <c r="H27" s="22" t="s">
+      <c r="H27" s="25" t="s">
         <v>50</v>
       </c>
-      <c r="I27" s="24">
+      <c r="I27" s="27">
         <v>1</v>
       </c>
     </row>
     <row r="28" spans="1:9">
-      <c r="H28" s="36" t="s">
+      <c r="H28" s="39" t="s">
         <v>31</v>
       </c>
-      <c r="I28" s="36">
+      <c r="I28" s="39">
         <v>25</v>
       </c>
     </row>
@@ -3206,27 +3221,27 @@
       </c>
     </row>
     <row r="31" spans="1:9">
-      <c r="A31" s="38" t="s">
+      <c r="A31" s="41" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="32" spans="1:9">
-      <c r="A32" s="38" t="s">
+      <c r="A32" s="41" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="33" spans="1:1">
-      <c r="A33" s="38" t="s">
+      <c r="A33" s="41" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="34" spans="1:1">
-      <c r="A34" s="38" t="s">
+      <c r="A34" s="41" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="35" spans="1:1">
-      <c r="A35" s="38" t="s">
+      <c r="A35" s="41" t="s">
         <v>56</v>
       </c>
     </row>
@@ -3474,12 +3489,12 @@
         <v>105</v>
       </c>
       <c r="K8" s="17" t="s">
-        <v>15</v>
+        <v>106</v>
       </c>
     </row>
     <row r="9" ht="88" customHeight="1" spans="1:11">
       <c r="A9" s="3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B9" s="4" t="s">
         <v>38</v>
@@ -3488,25 +3503,25 @@
         <v>16</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="J9" s="4" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="K9" s="15" t="s">
         <v>25</v>
@@ -3514,7 +3529,7 @@
     </row>
     <row r="10" ht="88" customHeight="1" spans="1:11">
       <c r="A10" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B10" s="4" t="s">
         <v>37</v>
@@ -3523,33 +3538,33 @@
         <v>21</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="I10" s="4" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="J10" s="4" t="s">
-        <v>121</v>
-      </c>
-      <c r="K10" s="17" t="s">
-        <v>15</v>
+        <v>122</v>
+      </c>
+      <c r="K10" s="19" t="s">
+        <v>123</v>
       </c>
     </row>
     <row r="11" ht="88" customHeight="1" spans="1:11">
       <c r="A11" s="3" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B11" s="4" t="s">
         <v>40</v>
@@ -3558,33 +3573,33 @@
         <v>16</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="I11" s="4" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="J11" s="4" t="s">
-        <v>129</v>
-      </c>
-      <c r="K11" s="17" t="s">
-        <v>15</v>
+        <v>131</v>
+      </c>
+      <c r="K11" s="15" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="12" ht="88" customHeight="1" spans="1:11">
       <c r="A12" s="3" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B12" s="4" t="s">
         <v>40</v>
@@ -3593,33 +3608,33 @@
         <v>21</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="E12" s="4" t="s">
         <v>100</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="I12" s="4" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="J12" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="K12" s="17" t="s">
-        <v>15</v>
+        <v>138</v>
+      </c>
+      <c r="K12" s="19" t="s">
+        <v>123</v>
       </c>
     </row>
     <row r="13" ht="88" customHeight="1" spans="1:11">
       <c r="A13" s="3" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B13" s="4" t="s">
         <v>36</v>
@@ -3628,33 +3643,33 @@
         <v>16</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="I13" s="4" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="J13" s="4" t="s">
-        <v>144</v>
-      </c>
-      <c r="K13" s="17" t="s">
-        <v>15</v>
+        <v>146</v>
+      </c>
+      <c r="K13" s="15" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="14" ht="88" customHeight="1" spans="1:11">
       <c r="A14" s="3" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="B14" s="4" t="s">
         <v>36</v>
@@ -3663,68 +3678,68 @@
         <v>21</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="I14" s="4" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="J14" s="4" t="s">
-        <v>152</v>
-      </c>
-      <c r="K14" s="17" t="s">
-        <v>15</v>
+        <v>154</v>
+      </c>
+      <c r="K14" s="20" t="s">
+        <v>155</v>
       </c>
     </row>
     <row r="15" ht="88" customHeight="1" spans="1:11">
       <c r="A15" s="3" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="B15" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="C15" s="19" t="s">
+      <c r="C15" s="21" t="s">
         <v>26</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="H15" s="4" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="J15" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="K15" s="17" t="s">
+        <v>163</v>
+      </c>
+      <c r="K15" s="22" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="16" ht="88" customHeight="1" spans="1:11">
       <c r="A16" s="3" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="B16" s="4" t="s">
         <v>41</v>
@@ -3733,68 +3748,68 @@
         <v>21</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="H16" s="4" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="I16" s="4" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="J16" s="4" t="s">
-        <v>168</v>
-      </c>
-      <c r="K16" s="17" t="s">
+        <v>171</v>
+      </c>
+      <c r="K16" s="22" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="17" ht="88" customHeight="1" spans="1:11">
       <c r="A17" s="3" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="B17" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="C17" s="19" t="s">
+      <c r="C17" s="21" t="s">
         <v>26</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="H17" s="4" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="I17" s="4" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="J17" s="4" t="s">
-        <v>176</v>
-      </c>
-      <c r="K17" s="17" t="s">
-        <v>15</v>
+        <v>179</v>
+      </c>
+      <c r="K17" s="19" t="s">
+        <v>180</v>
       </c>
     </row>
     <row r="18" ht="88" customHeight="1" spans="1:11">
       <c r="A18" s="3" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="B18" s="4" t="s">
         <v>42</v>
@@ -3803,33 +3818,33 @@
         <v>21</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="G18" s="4" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="H18" s="4" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="I18" s="4" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="J18" s="4" t="s">
-        <v>184</v>
-      </c>
-      <c r="K18" s="17" t="s">
+        <v>188</v>
+      </c>
+      <c r="K18" s="22" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="19" ht="88" customHeight="1" spans="1:11">
       <c r="A19" s="3" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="B19" s="4" t="s">
         <v>45</v>
@@ -3838,68 +3853,68 @@
         <v>21</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="G19" s="4" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="H19" s="4" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="I19" s="4" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="J19" s="4" t="s">
-        <v>192</v>
-      </c>
-      <c r="K19" s="17" t="s">
+        <v>196</v>
+      </c>
+      <c r="K19" s="22" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="20" ht="88" customHeight="1" spans="1:11">
       <c r="A20" s="3" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="B20" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="C20" s="19" t="s">
+      <c r="C20" s="21" t="s">
         <v>26</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="G20" s="4" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="H20" s="4" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="I20" s="4" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="J20" s="4" t="s">
-        <v>200</v>
-      </c>
-      <c r="K20" s="17" t="s">
+        <v>204</v>
+      </c>
+      <c r="K20" s="22" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="21" ht="88" customHeight="1" spans="1:11">
       <c r="A21" s="3" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="B21" s="4" t="s">
         <v>47</v>
@@ -3908,68 +3923,68 @@
         <v>21</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="G21" s="4" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="H21" s="4" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="I21" s="4" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="J21" s="4" t="s">
-        <v>208</v>
-      </c>
-      <c r="K21" s="17" t="s">
+        <v>212</v>
+      </c>
+      <c r="K21" s="22" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="22" ht="88" customHeight="1" spans="1:11">
       <c r="A22" s="3" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="B22" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="C22" s="19" t="s">
+      <c r="C22" s="21" t="s">
         <v>26</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="E22" s="4" t="s">
         <v>100</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="G22" s="4" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="H22" s="4" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="I22" s="4" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="J22" s="4" t="s">
-        <v>215</v>
-      </c>
-      <c r="K22" s="17" t="s">
+        <v>219</v>
+      </c>
+      <c r="K22" s="22" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="23" ht="88" customHeight="1" spans="1:11">
       <c r="A23" s="3" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="B23" s="4" t="s">
         <v>39</v>
@@ -3978,33 +3993,33 @@
         <v>21</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="G23" s="4" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="H23" s="4" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="I23" s="4" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="J23" s="4" t="s">
-        <v>223</v>
-      </c>
-      <c r="K23" s="17" t="s">
+        <v>227</v>
+      </c>
+      <c r="K23" s="22" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="24" ht="88" customHeight="1" spans="1:11">
       <c r="A24" s="3" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="B24" s="4" t="s">
         <v>43</v>
@@ -4013,33 +4028,33 @@
         <v>21</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="G24" s="4" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="H24" s="4" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="I24" s="4" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="J24" s="4" t="s">
-        <v>231</v>
-      </c>
-      <c r="K24" s="17" t="s">
+        <v>235</v>
+      </c>
+      <c r="K24" s="22" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="25" ht="88" customHeight="1" spans="1:11">
       <c r="A25" s="3" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="B25" s="4" t="s">
         <v>37</v>
@@ -4048,103 +4063,103 @@
         <v>16</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="G25" s="4" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="H25" s="4" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="I25" s="4" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="J25" s="4" t="s">
-        <v>239</v>
-      </c>
-      <c r="K25" s="17" t="s">
-        <v>15</v>
+        <v>243</v>
+      </c>
+      <c r="K25" s="19" t="s">
+        <v>123</v>
       </c>
     </row>
     <row r="26" ht="88" customHeight="1" spans="1:11">
       <c r="A26" s="3" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="B26" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="C26" s="19" t="s">
+      <c r="C26" s="21" t="s">
         <v>26</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="G26" s="4" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="H26" s="4" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="I26" s="4" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="J26" s="4" t="s">
-        <v>247</v>
-      </c>
-      <c r="K26" s="17" t="s">
+        <v>251</v>
+      </c>
+      <c r="K26" s="22" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="27" ht="88" customHeight="1" spans="1:11">
       <c r="A27" s="3" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="B27" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="C27" s="19" t="s">
+      <c r="C27" s="21" t="s">
         <v>26</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="G27" s="4" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="H27" s="4" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="I27" s="4" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="J27" s="4" t="s">
-        <v>255</v>
-      </c>
-      <c r="K27" s="17" t="s">
+        <v>259</v>
+      </c>
+      <c r="K27" s="22" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="28" ht="88" customHeight="1" spans="1:11">
       <c r="A28" s="3" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="B28" s="4" t="s">
         <v>50</v>
@@ -4153,27 +4168,27 @@
         <v>21</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="G28" s="4" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="H28" s="4" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="I28" s="4" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="J28" s="4" t="s">
-        <v>263</v>
-      </c>
-      <c r="K28" s="17" t="s">
+        <v>267</v>
+      </c>
+      <c r="K28" s="22" t="s">
         <v>15</v>
       </c>
     </row>
@@ -4207,18 +4222,18 @@
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:8">
       <c r="A1" s="1" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:8">
       <c r="A3" s="2" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>59</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>61</v>
@@ -4230,33 +4245,33 @@
         <v>64</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="4" ht="34" customHeight="1" spans="1:8">
       <c r="A4" s="3" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>36</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="H4" s="7" t="s">
         <v>68</v>
@@ -4264,25 +4279,25 @@
     </row>
     <row r="5" ht="34" customHeight="1" spans="1:8">
       <c r="A5" s="3" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="B5" s="4" t="s">
         <v>36</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="F5" s="4" t="s">
+        <v>282</v>
+      </c>
+      <c r="G5" s="6" t="s">
         <v>278</v>
-      </c>
-      <c r="G5" s="6" t="s">
-        <v>274</v>
       </c>
       <c r="H5" s="7" t="s">
         <v>68</v>
@@ -4290,207 +4305,207 @@
     </row>
     <row r="6" ht="34" customHeight="1" spans="1:8">
       <c r="A6" s="3" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="B6" s="4" t="s">
         <v>36</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="H6" s="7" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
     </row>
     <row r="7" ht="34" customHeight="1" spans="1:8">
       <c r="A7" s="3" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="B7" s="4" t="s">
         <v>36</v>
       </c>
       <c r="C7" s="5" t="s">
+        <v>289</v>
+      </c>
+      <c r="D7" s="4" t="s">
         <v>285</v>
       </c>
-      <c r="D7" s="4" t="s">
-        <v>281</v>
-      </c>
       <c r="E7" s="4" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="H7" s="7" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
     </row>
     <row r="8" ht="34" customHeight="1" spans="1:8">
       <c r="A8" s="3" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="B8" s="4" t="s">
         <v>36</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="E8" s="4" t="s">
+        <v>296</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>297</v>
+      </c>
+      <c r="G8" s="8" t="s">
         <v>292</v>
       </c>
-      <c r="F8" s="4" t="s">
+      <c r="H8" s="7" t="s">
         <v>293</v>
-      </c>
-      <c r="G8" s="8" t="s">
-        <v>288</v>
-      </c>
-      <c r="H8" s="7" t="s">
-        <v>289</v>
       </c>
     </row>
     <row r="9" ht="34" customHeight="1" spans="1:8">
       <c r="A9" s="3" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="B9" s="4" t="s">
         <v>36</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="H9" s="7" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
     </row>
     <row r="10" ht="34" customHeight="1" spans="1:8">
       <c r="A10" s="3" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="B10" s="4" t="s">
         <v>40</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="H10" s="7" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
     </row>
     <row r="11" ht="34" customHeight="1" spans="1:8">
       <c r="A11" s="3" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="B11" s="4" t="s">
         <v>40</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="H11" s="7" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="12" ht="34" customHeight="1" spans="1:8">
       <c r="A12" s="3" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="B12" s="4" t="s">
         <v>40</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="G12" s="8" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="H12" s="7" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
     </row>
     <row r="13" ht="34" customHeight="1" spans="1:8">
       <c r="A13" s="3" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="B13" s="4" t="s">
         <v>37</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="G13" s="6" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="H13" s="7" t="s">
         <v>76</v>
@@ -4498,155 +4513,155 @@
     </row>
     <row r="14" ht="34" customHeight="1" spans="1:8">
       <c r="A14" s="3" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="B14" s="4" t="s">
         <v>37</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="G14" s="8" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="H14" s="7" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
     </row>
     <row r="15" ht="34" customHeight="1" spans="1:8">
       <c r="A15" s="3" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="B15" s="4" t="s">
         <v>37</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="H15" s="7" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
     </row>
     <row r="16" ht="34" customHeight="1" spans="1:8">
       <c r="A16" s="3" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="B16" s="4" t="s">
         <v>37</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="H16" s="7" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
     </row>
     <row r="17" ht="34" customHeight="1" spans="1:8">
       <c r="A17" s="3" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="B17" s="4" t="s">
         <v>37</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="G17" s="6" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="H17" s="7" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="18" ht="34" customHeight="1" spans="1:8">
       <c r="A18" s="3" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="B18" s="4" t="s">
         <v>37</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="G18" s="8" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="H18" s="7" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
     </row>
     <row r="19" ht="34" customHeight="1" spans="1:8">
       <c r="A19" s="3" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="B19" s="4" t="s">
         <v>39</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="G19" s="6" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="H19" s="7" t="s">
         <v>91</v>
@@ -4654,259 +4669,259 @@
     </row>
     <row r="20" ht="34" customHeight="1" spans="1:8">
       <c r="A20" s="3" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="B20" s="4" t="s">
         <v>39</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="G20" s="8" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="H20" s="7" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
     </row>
     <row r="21" ht="34" customHeight="1" spans="1:8">
       <c r="A21" s="3" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="B21" s="4" t="s">
         <v>39</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="G21" s="6" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="H21" s="7" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
     </row>
     <row r="22" ht="34" customHeight="1" spans="1:8">
       <c r="A22" s="3" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="B22" s="4" t="s">
         <v>39</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="G22" s="8" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="H22" s="7" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
     </row>
     <row r="23" ht="34" customHeight="1" spans="1:8">
       <c r="A23" s="3" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="G23" s="8" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="H23" s="7" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
     </row>
     <row r="24" ht="34" customHeight="1" spans="1:8">
       <c r="A24" s="3" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="G24" s="8" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="H24" s="7" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
     </row>
     <row r="25" ht="34" customHeight="1" spans="1:8">
       <c r="A25" s="3" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="G25" s="8" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="H25" s="7" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
     </row>
     <row r="26" ht="34" customHeight="1" spans="1:8">
       <c r="A26" s="3" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="B26" s="4" t="s">
         <v>41</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="H26" s="7" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
     </row>
     <row r="27" ht="34" customHeight="1" spans="1:8">
       <c r="A27" s="3" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="B27" s="4" t="s">
         <v>41</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="G27" s="8" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="H27" s="7" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
     </row>
     <row r="28" ht="34" customHeight="1" spans="1:8">
       <c r="A28" s="3" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="B28" s="4" t="s">
         <v>41</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="H28" s="7" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
     </row>
     <row r="29" ht="34" customHeight="1" spans="1:8">
       <c r="A29" s="3" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="B29" s="4" t="s">
         <v>38</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="G29" s="6" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="H29" s="7" t="s">
         <v>84</v>
@@ -4914,129 +4929,129 @@
     </row>
     <row r="30" ht="34" customHeight="1" spans="1:8">
       <c r="A30" s="3" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="B30" s="4" t="s">
         <v>38</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="H30" s="7" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="31" ht="34" customHeight="1" spans="1:8">
       <c r="A31" s="3" t="s">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="B31" s="4" t="s">
         <v>43</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="F31" s="4" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="G31" s="9" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="H31" s="7" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
     </row>
     <row r="32" ht="34" customHeight="1" spans="1:8">
       <c r="A32" s="3" t="s">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="B32" s="4" t="s">
         <v>43</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="G32" s="8" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="H32" s="7" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
     </row>
     <row r="33" ht="34" customHeight="1" spans="1:8">
       <c r="A33" s="3" t="s">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="B33" s="4" t="s">
         <v>43</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="F33" s="4" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="G33" s="8" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="H33" s="7" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
     </row>
     <row r="34" ht="34" customHeight="1" spans="1:8">
       <c r="A34" s="3" t="s">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="B34" s="4" t="s">
         <v>44</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="D34" s="4" t="s">
         <v>100</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="F34" s="4" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="H34" s="7" t="s">
         <v>98</v>
@@ -5044,400 +5059,400 @@
     </row>
     <row r="35" ht="34" customHeight="1" spans="1:8">
       <c r="A35" s="3" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="B35" s="4" t="s">
         <v>46</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="E35" s="4" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="F35" s="4" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="G35" s="8" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="H35" s="7" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
     </row>
     <row r="36" ht="34" customHeight="1" spans="1:8">
       <c r="A36" s="3" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c r="B36" s="4" t="s">
         <v>46</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>425</v>
+        <v>429</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="E36" s="4" t="s">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="F36" s="4" t="s">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="H36" s="7" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
     </row>
     <row r="37" ht="34" customHeight="1" spans="1:8">
       <c r="A37" s="3" t="s">
-        <v>429</v>
+        <v>433</v>
       </c>
       <c r="B37" s="4" t="s">
         <v>45</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="E37" s="4" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="F37" s="4" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="G37" s="8" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="H37" s="7" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
     </row>
     <row r="38" ht="34" customHeight="1" spans="1:8">
       <c r="A38" s="3" t="s">
-        <v>434</v>
+        <v>438</v>
       </c>
       <c r="B38" s="4" t="s">
         <v>45</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>436</v>
+        <v>440</v>
       </c>
       <c r="E38" s="4" t="s">
-        <v>437</v>
+        <v>441</v>
       </c>
       <c r="F38" s="4" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="H38" s="7" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
     </row>
     <row r="39" ht="34" customHeight="1" spans="1:8">
       <c r="A39" s="3" t="s">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="B39" s="4" t="s">
         <v>45</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
       <c r="E39" s="4" t="s">
-        <v>442</v>
+        <v>446</v>
       </c>
       <c r="F39" s="4" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="G39" s="8" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="H39" s="7" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
     </row>
     <row r="40" ht="34" customHeight="1" spans="1:8">
       <c r="A40" s="3" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="E40" s="4" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="F40" s="4" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="H40" s="7" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
     </row>
     <row r="41" ht="34" customHeight="1" spans="1:8">
       <c r="A41" s="3" t="s">
-        <v>450</v>
+        <v>454</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>452</v>
+        <v>456</v>
       </c>
       <c r="E41" s="4" t="s">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="F41" s="4" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="G41" s="8" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="H41" s="7" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
     </row>
     <row r="42" ht="34" customHeight="1" spans="1:8">
       <c r="A42" s="3" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="B42" s="4" t="s">
         <v>42</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="D42" s="4" t="s">
-        <v>456</v>
+        <v>460</v>
       </c>
       <c r="E42" s="4" t="s">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="F42" s="4" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="G42" s="8" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="H42" s="7" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
     </row>
     <row r="43" ht="34" customHeight="1" spans="1:8">
       <c r="A43" s="3" t="s">
-        <v>458</v>
+        <v>462</v>
       </c>
       <c r="B43" s="4" t="s">
         <v>42</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="E43" s="4" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="F43" s="4" t="s">
-        <v>462</v>
+        <v>466</v>
       </c>
       <c r="G43" s="6" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="H43" s="7" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
     </row>
     <row r="44" ht="34" customHeight="1" spans="1:8">
       <c r="A44" s="3" t="s">
-        <v>463</v>
+        <v>467</v>
       </c>
       <c r="B44" s="4" t="s">
         <v>42</v>
       </c>
       <c r="C44" s="5" t="s">
+        <v>468</v>
+      </c>
+      <c r="D44" s="4" t="s">
         <v>464</v>
       </c>
-      <c r="D44" s="4" t="s">
-        <v>460</v>
-      </c>
       <c r="E44" s="4" t="s">
-        <v>465</v>
+        <v>469</v>
       </c>
       <c r="F44" s="4" t="s">
-        <v>466</v>
+        <v>470</v>
       </c>
       <c r="G44" s="8" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="H44" s="7" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
     </row>
     <row r="45" ht="34" customHeight="1" spans="1:8">
       <c r="A45" s="3" t="s">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="B45" s="4" t="s">
         <v>47</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>468</v>
+        <v>472</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="E45" s="4" t="s">
-        <v>470</v>
+        <v>474</v>
       </c>
       <c r="F45" s="4" t="s">
-        <v>471</v>
+        <v>475</v>
       </c>
       <c r="G45" s="6" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="H45" s="7" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
     </row>
     <row r="46" ht="34" customHeight="1" spans="1:8">
       <c r="A46" s="3" t="s">
-        <v>472</v>
+        <v>476</v>
       </c>
       <c r="B46" s="4" t="s">
         <v>47</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>473</v>
+        <v>477</v>
       </c>
       <c r="D46" s="4" t="s">
-        <v>474</v>
+        <v>478</v>
       </c>
       <c r="E46" s="4" t="s">
-        <v>475</v>
+        <v>479</v>
       </c>
       <c r="F46" s="4" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="G46" s="8" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="H46" s="7" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
     </row>
     <row r="47" ht="34" customHeight="1" spans="1:8">
       <c r="A47" s="3" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="B47" s="4" t="s">
         <v>50</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>478</v>
+        <v>482</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>479</v>
+        <v>483</v>
       </c>
       <c r="E47" s="4" t="s">
-        <v>480</v>
+        <v>484</v>
       </c>
       <c r="F47" s="4" t="s">
-        <v>481</v>
+        <v>485</v>
       </c>
       <c r="G47" s="6" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="H47" s="7" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
     </row>
     <row r="48" ht="34" customHeight="1" spans="1:8">
       <c r="A48" s="3" t="s">
-        <v>482</v>
+        <v>486</v>
       </c>
       <c r="B48" s="4" t="s">
         <v>48</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>483</v>
+        <v>487</v>
       </c>
       <c r="D48" s="4" t="s">
         <v>100</v>
       </c>
       <c r="E48" s="4" t="s">
-        <v>484</v>
+        <v>488</v>
       </c>
       <c r="F48" s="4" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="H48" s="7" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
     </row>
     <row r="49" ht="34" customHeight="1" spans="1:8">
       <c r="A49" s="3" t="s">
-        <v>486</v>
+        <v>490</v>
       </c>
       <c r="B49" s="4" t="s">
         <v>43</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>487</v>
+        <v>491</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="E49" s="4" t="s">
-        <v>489</v>
+        <v>493</v>
       </c>
       <c r="F49" s="4" t="s">
-        <v>490</v>
+        <v>494</v>
       </c>
       <c r="G49" s="9" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="H49" s="7" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
     </row>
     <row r="51" spans="1:8">
       <c r="A51" s="10" t="s">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="B51" s="11" t="s">
-        <v>492</v>
+        <v>496</v>
       </c>
       <c r="C51" s="11">
         <v>46</v>
@@ -5446,7 +5461,7 @@
     <row r="52" spans="1:8">
       <c r="A52" s="12"/>
       <c r="B52" s="12" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="C52" s="12">
         <v>23</v>
@@ -5455,7 +5470,7 @@
     <row r="53" spans="1:8">
       <c r="A53" s="12"/>
       <c r="B53" s="12" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="C53" s="12">
         <v>21</v>
@@ -5464,7 +5479,7 @@
     <row r="54" spans="1:8">
       <c r="A54" s="12"/>
       <c r="B54" s="12" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="C54" s="12">
         <v>2</v>
@@ -5473,7 +5488,7 @@
     <row r="55" spans="1:8">
       <c r="A55" s="12"/>
       <c r="B55" s="12" t="s">
-        <v>493</v>
+        <v>497</v>
       </c>
       <c r="C55" s="13">
         <v>0.543478260869565</v>
